--- a/frontend/meal_menu_template.xlsx
+++ b/frontend/meal_menu_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Me\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prj\maryam-hostel\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38E6967-DFA4-40B5-B124-F2D808107C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D16E90B-7E86-434E-B468-D245BE30CB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,12 @@
     <sheet name="Meals" sheetId="2" r:id="rId2"/>
     <sheet name="Schedule" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="102">
   <si>
     <t>Name</t>
   </si>
@@ -87,54 +87,6 @@
     <t>Prep Time (mins)</t>
   </si>
   <si>
-    <t>Paratha &amp; Chai</t>
-  </si>
-  <si>
-    <t>Fresh homemade paratha with masala chai</t>
-  </si>
-  <si>
-    <t>Vegetarian</t>
-  </si>
-  <si>
-    <t>Chicken Biryani</t>
-  </si>
-  <si>
-    <t>Aromatic basmati rice with chicken</t>
-  </si>
-  <si>
-    <t>Halal</t>
-  </si>
-  <si>
-    <t>Chicken Karahi</t>
-  </si>
-  <si>
-    <t>Spicy chicken karahi with naan</t>
-  </si>
-  <si>
-    <t>Bread &amp; Omelette</t>
-  </si>
-  <si>
-    <t>Toasted bread with fluffy omelette</t>
-  </si>
-  <si>
-    <t>Vegetarian, High Prot</t>
-  </si>
-  <si>
-    <t>Rice &amp; Curry</t>
-  </si>
-  <si>
-    <t>Steamed rice with vegetable curry</t>
-  </si>
-  <si>
-    <t>Vegetarian, Halal</t>
-  </si>
-  <si>
-    <t>Pasta</t>
-  </si>
-  <si>
-    <t>Creamy pasta with vegetables</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -153,40 +105,238 @@
     <t>Special Note</t>
   </si>
   <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
     <t>MARYAM HOSTLE ISB</t>
   </si>
   <si>
-    <t>2026-08-25</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>2026-08-29</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Omelette or Half fry with Paratha plus Tea and Achaar</t>
+  </si>
+  <si>
+    <t>Bread with Jam and Porridge plus Tea</t>
+  </si>
+  <si>
+    <t>Aloo Bhujiya with Paratha plus Tea and Achaar</t>
+  </si>
+  <si>
+    <t>French Toast and Porridge plus Tea</t>
+  </si>
+  <si>
+    <t>Yogurt with Paratha plus Tea and Achaar</t>
+  </si>
+  <si>
+    <t>Halwa Puri With Chana plus Tea and Achaar</t>
+  </si>
+  <si>
+    <t>Aloo Paratha plus Tea and Achaar</t>
+  </si>
+  <si>
+    <t>Chicken Qorma or Chicken Karahi with Roti and Salad</t>
+  </si>
+  <si>
+    <t>Chana Pulao or Sabzi Pulao with Shami Kebab and Raita</t>
+  </si>
+  <si>
+    <t>Beef Nihari with Roti, Salad and Sweet Dish</t>
+  </si>
+  <si>
+    <t>Chicken Haleem with Garnish and Roti</t>
+  </si>
+  <si>
+    <t>Chicken Biryani with traditional Raita and Cold Drink</t>
+  </si>
+  <si>
+    <t>Mix Sabzi and Daal with Rice and Roti</t>
+  </si>
+  <si>
+    <t>Desi Nashta</t>
+  </si>
+  <si>
+    <t>Chicken fever</t>
+  </si>
+  <si>
+    <t>Vegies day</t>
+  </si>
+  <si>
+    <t>Beef energy</t>
+  </si>
+  <si>
+    <t>English style</t>
+  </si>
+  <si>
+    <t>Haleem season</t>
+  </si>
+  <si>
+    <t>Healthy start</t>
+  </si>
+  <si>
+    <t>Tasty Biryani</t>
+  </si>
+  <si>
+    <t>Lahori Nashta</t>
+  </si>
+  <si>
+    <t>Aloo Chicken Keema with Roti or Macaroni</t>
+  </si>
+  <si>
+    <t>Mother's touch</t>
+  </si>
+  <si>
+    <t>Truck adda</t>
+  </si>
+  <si>
+    <t>Live Healthy</t>
+  </si>
+  <si>
+    <t>Spot meal</t>
+  </si>
+  <si>
+    <t>Instant meal</t>
+  </si>
+  <si>
+    <t>High Protein (chicken), High Carb (roti), High Fat (curry/oil)</t>
+  </si>
+  <si>
+    <t>High Protein (eggs), High Carb (paratha), Moderate Fat</t>
+  </si>
+  <si>
+    <t>High Carb (bread, jam, porridge), Low Protein, Low Fat</t>
+  </si>
+  <si>
+    <t>High Protein (kebab, chickpeas), High Carb (rice), Moderate Fat</t>
+  </si>
+  <si>
+    <t>High Carb (paratha, potatoes), Moderate Fat (oil), Low Protein</t>
+  </si>
+  <si>
+    <t>High Protein (beef), High Fat (Nihari is oily), High Carb (roti + dessert), High Sugar (sweet dish)</t>
+  </si>
+  <si>
+    <t>High Carb (bread, porridge, jam/sugar), Moderate Protein (eggs, milk), Moderate </t>
+  </si>
+  <si>
+    <t>High Protein (chicken, lentils), High Carb (wheat, roti), Moderate Fat</t>
+  </si>
+  <si>
+    <t>High Carb (paratha), Moderate Protein (yogurt), Moderate Fat</t>
+  </si>
+  <si>
+    <t>High Protein (chicken), High Carb (rice), High Sugar (cold drink), Moderate Fat</t>
+  </si>
+  <si>
+    <t>High Carb (puri, halwa), High Sugar (halwa), Moderate Protein (chana), High Fat (fried puri)</t>
+  </si>
+  <si>
+    <t>High Protein (chicken keema), High Carb (roti/pasta), Moderate Fat</t>
+  </si>
+  <si>
+    <t>High Carb (potatoes, wheat), Moderate Fat (fried), Low Protein</t>
+  </si>
+  <si>
+    <t>High Carb (rice, roti), Moderate Protein (daal/lentils), Low Fat (unless tempered with ghee)</t>
+  </si>
+  <si>
+    <t>Bonjour Madam</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -216,8 +366,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,13 +752,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="41" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="4" max="4" width="86.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -630,50 +781,47 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
       <c r="E3">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>45</v>
@@ -681,7 +829,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
@@ -690,44 +838,281 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
       <c r="E6">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s">
         <v>35</v>
       </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7">
-        <v>35</v>
+      <c r="C20" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -737,330 +1122,1611 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
         <v>43</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
         <v>44</v>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s">
         <v>43</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" t="s">
         <v>44</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="E28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" t="s">
+        <v>42</v>
+      </c>
+      <c r="E44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" t="s">
         <v>43</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E46" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" t="s">
         <v>44</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="E49" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" t="s">
+        <v>42</v>
+      </c>
+      <c r="E50" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" t="s">
+        <v>56</v>
+      </c>
+      <c r="E51" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" t="s">
+        <v>71</v>
+      </c>
+      <c r="E53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" t="s">
+        <v>56</v>
+      </c>
+      <c r="E54" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" t="s">
+        <v>47</v>
+      </c>
+      <c r="E55" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B56" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" t="s">
+        <v>48</v>
+      </c>
+      <c r="E56" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" t="s">
+        <v>56</v>
+      </c>
+      <c r="E57" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" t="s">
+        <v>49</v>
+      </c>
+      <c r="E58" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B59" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>50</v>
+      </c>
+      <c r="E59" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" t="s">
+        <v>56</v>
+      </c>
+      <c r="E60" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B61" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="E61" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B62" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" t="s">
+        <v>53</v>
+      </c>
+      <c r="E62" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" t="s">
+        <v>56</v>
+      </c>
+      <c r="E63" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" t="s">
+        <v>54</v>
+      </c>
+      <c r="E64" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" t="s">
+        <v>42</v>
+      </c>
+      <c r="E65" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B66" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>56</v>
+      </c>
+      <c r="E66" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B67" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" t="s">
+        <v>43</v>
+      </c>
+      <c r="E67" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" t="s">
+        <v>46</v>
+      </c>
+      <c r="E68" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" t="s">
+        <v>56</v>
+      </c>
+      <c r="E69" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B70" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E70" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B71" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" t="s">
+        <v>42</v>
+      </c>
+      <c r="E71" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B72" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" t="s">
+        <v>56</v>
+      </c>
+      <c r="E72" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B73" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" t="s">
         <v>45</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E73" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" t="s">
+        <v>71</v>
+      </c>
+      <c r="E74" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B75" t="s">
+        <v>27</v>
+      </c>
+      <c r="C75" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" t="s">
+        <v>56</v>
+      </c>
+      <c r="E75" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B76" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" t="s">
+        <v>47</v>
+      </c>
+      <c r="E76" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" t="s">
+        <v>48</v>
+      </c>
+      <c r="E77" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B78" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" t="s">
+        <v>56</v>
+      </c>
+      <c r="E78" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B79" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" t="s">
+        <v>49</v>
+      </c>
+      <c r="E79" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B80" t="s">
+        <v>27</v>
+      </c>
+      <c r="C80" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" t="s">
+        <v>50</v>
+      </c>
+      <c r="E80" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B81" t="s">
+        <v>27</v>
+      </c>
+      <c r="C81" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" t="s">
+        <v>56</v>
+      </c>
+      <c r="E81" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B82" t="s">
+        <v>27</v>
+      </c>
+      <c r="C82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" t="s">
+        <v>52</v>
+      </c>
+      <c r="E82" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B83" t="s">
+        <v>27</v>
+      </c>
+      <c r="C83" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" t="s">
+        <v>53</v>
+      </c>
+      <c r="E83" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B84" t="s">
+        <v>27</v>
+      </c>
+      <c r="C84" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" t="s">
+        <v>56</v>
+      </c>
+      <c r="E84" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B85" t="s">
+        <v>27</v>
+      </c>
+      <c r="C85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" t="s">
+        <v>54</v>
+      </c>
+      <c r="E85" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B86" t="s">
+        <v>27</v>
+      </c>
+      <c r="C86" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" t="s">
+        <v>42</v>
+      </c>
+      <c r="E86" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B87" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" t="s">
+        <v>56</v>
+      </c>
+      <c r="E87" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B88" t="s">
+        <v>27</v>
+      </c>
+      <c r="C88" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" t="s">
+        <v>43</v>
+      </c>
+      <c r="E88" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B89" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" t="s">
+        <v>46</v>
+      </c>
+      <c r="E89" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B90" t="s">
+        <v>27</v>
+      </c>
+      <c r="C90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E90" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B91" t="s">
+        <v>27</v>
+      </c>
+      <c r="C91" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" t="s">
         <v>44</v>
       </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" t="s">
-        <v>52</v>
-      </c>
+      <c r="E91" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="1"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="1"/>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="1"/>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="1"/>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="1"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="1"/>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="1"/>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
